--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_1504.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_1504.xlsx
@@ -1376,6 +1376,9 @@
       <c r="E16" t="n">
         <v>2.125</v>
       </c>
+      <c r="H16" t="n">
+        <v>1.72</v>
+      </c>
       <c r="I16" t="n">
         <v>1.9</v>
       </c>
@@ -1394,12 +1397,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: CHEX@HEX, THDMAJ_A1@DRIVE, THDMAJ_A@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1504-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: CHEX@HEX, THDMAJ_A1@DRIVE, THDMAJ_A@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1504-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1504-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 1504-24-24-FG (PARTcommunity / CADENAS, CHEX@HEX=C, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A@DRIVE=A1THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1504-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 1504-24-24-FG (PARTcommunity / CADENAS, CHEX@HEX=C, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A@DRIVE=A1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1424,6 +1427,9 @@
           <t>1504-32-32-FG</t>
         </is>
       </c>
+      <c r="H17" t="n">
+        <v>2.2</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>1504-32-32-FG</t>
@@ -1436,12 +1442,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
